--- a/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
@@ -95,7 +95,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Sheet1">
+  <sheet name="Sheet1" bannerRows="1">
     <column index="1" property="Name"/>
     <column index="2" property="Team"/>
   </sheet>

--- a/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
@@ -54,7 +54,7 @@
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Imported data - do not edit.</t>
@@ -88,7 +88,7 @@
   </sheetData>
   <autoFilter ref="A2:B3"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:XFD1"/>
   </mergeCells>
 </worksheet>
 </file>

--- a/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
@@ -95,7 +95,7 @@
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
-  <sheet name="Sheet1" bannerRows="1">
+  <sheet name="Sheet1" banner="true">
     <column index="1" property="Name"/>
     <column index="2" property="Team"/>
   </sheet>

--- a/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
+++ b/src/Excelsior.Tests/BannerTests.DictionarySheetBanner.verified.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1" banner="true">
     <column index="1" property="Name"/>
     <column index="2" property="Team"/>
